--- a/assignment/project/셔틀_이용기록.xlsx
+++ b/assignment/project/셔틀_이용기록.xlsx
@@ -12664,11 +12664,11 @@
   </sheetData>
   <autoFilter ref="$A$1:$K$1001"/>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="목록에서 선택합니다. 다른 정류장은 이름을 직접 적어도 됩니다." sqref="D2:D1001 I2:I1001">
-      <formula1>"반도체대학,교육대학원,AI공학관,예체대"</formula1>
-    </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" prompt="0 이상의 숫자입니다. 모르면 비워 둡니다." sqref="E2:H1001 J2:K1001">
       <formula1>0.0</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" prompt="목록에서 선택합니다. 다른 정류장은 이름을 직접 적어도 됩니다." sqref="D2:D1001 I2:I1001">
+      <formula1>"반도체대학,교육대학원,AI공학관,예체대,학생회관"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions/>
